--- a/data/ExampleExcelFile.xlsx
+++ b/data/ExampleExcelFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peyto\Documents\work_capacity_project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E60D5D-4BBD-4285-AE7B-6D1769821CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B160ABFB-6586-4A0D-B9E9-D3BCEE3778CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{F74EBD9B-CB49-4A22-B5FE-A2696EA9C09F}"/>
   </bookViews>
@@ -626,7 +626,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <v>100</v>

--- a/data/ExampleExcelFile.xlsx
+++ b/data/ExampleExcelFile.xlsx
@@ -8,15 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peyto\Documents\work_capacity_project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B160ABFB-6586-4A0D-B9E9-D3BCEE3778CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCB4753-1ADB-4306-B228-0D4D0259EF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{F74EBD9B-CB49-4A22-B5FE-A2696EA9C09F}"/>
+    <workbookView xWindow="16020" yWindow="3885" windowWidth="19185" windowHeight="11265" activeTab="9" xr2:uid="{F74EBD9B-CB49-4A22-B5FE-A2696EA9C09F}"/>
   </bookViews>
   <sheets>
     <sheet name="Program Monthly Demand" sheetId="1" r:id="rId1"/>
     <sheet name="BOM" sheetId="2" r:id="rId2"/>
-    <sheet name="Route Information" sheetId="3" r:id="rId3"/>
+    <sheet name="Annual Max Limits" sheetId="5" r:id="rId3"/>
     <sheet name="Workcenter Information" sheetId="4" r:id="rId4"/>
+    <sheet name="Part Route Map" sheetId="6" r:id="rId5"/>
+    <sheet name="Route Information" sheetId="3" r:id="rId6"/>
+    <sheet name="TP Parameters" sheetId="7" r:id="rId7"/>
+    <sheet name="TP Workcenter" sheetId="8" r:id="rId8"/>
+    <sheet name="TP Router Operation" sheetId="9" r:id="rId9"/>
+    <sheet name="TP Part Router" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="61">
   <si>
     <t>Program</t>
   </si>
@@ -95,9 +101,6 @@
     <t>d6</t>
   </si>
   <si>
-    <t>Tasklist_Num</t>
-  </si>
-  <si>
     <t>Workcenter</t>
   </si>
   <si>
@@ -107,9 +110,6 @@
     <t>HPU</t>
   </si>
   <si>
-    <t>Route_Ratio</t>
-  </si>
-  <si>
     <t>wc1</t>
   </si>
   <si>
@@ -152,7 +152,85 @@
     <t>0100</t>
   </si>
   <si>
-    <t>Available_Hours</t>
+    <t>Max Annual Limit</t>
+  </si>
+  <si>
+    <t>Available Hours</t>
+  </si>
+  <si>
+    <t>Overtime Percentage</t>
+  </si>
+  <si>
+    <t>Capacity Count</t>
+  </si>
+  <si>
+    <t>Router</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>Limit</t>
+  </si>
+  <si>
+    <t>Creator</t>
+  </si>
+  <si>
+    <t>Sampling Rate</t>
+  </si>
+  <si>
+    <t>TP Parameter</t>
+  </si>
+  <si>
+    <t>Processing Rate</t>
+  </si>
+  <si>
+    <t>Route Percentage</t>
+  </si>
+  <si>
+    <t>Route Quantity</t>
+  </si>
+  <si>
+    <t>TP Level</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Router Operation</t>
+  </si>
+  <si>
+    <t>Part Router</t>
+  </si>
+  <si>
+    <t>Num Processing Units</t>
+  </si>
+  <si>
+    <t>Amount Processing Time</t>
+  </si>
+  <si>
+    <t>Percentage of Workable Overtime</t>
+  </si>
+  <si>
+    <t>The HPU modifier</t>
+  </si>
+  <si>
+    <t>Percentage of parts that use this route</t>
+  </si>
+  <si>
+    <t>The number of units to send to this route</t>
+  </si>
+  <si>
+    <t>The amount of parts that stop at this step</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>System</t>
   </si>
 </sst>
 </file>
@@ -798,6 +876,69 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E267EF03-D3A0-4D58-B789-74A149F9AF25}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46143</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{ABAD00DB-6EA9-404C-AB89-CA3F3E7CD10C}">
+          <x14:formula1>
+            <xm:f>'TP Parameters'!$A$7:$A$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B22C143-544B-45B9-9C78-661BA8F93D9E}">
   <dimension ref="A1:D12"/>
@@ -981,255 +1122,486 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4990E113-81AF-472E-91CF-319BAC24E8AB}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCB07F09-0C11-4BF9-8684-61C02A91D479}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2">
+        <v>80</v>
+      </c>
+      <c r="C2">
+        <v>0.15</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3">
+        <v>80</v>
+      </c>
+      <c r="C3">
+        <v>0.15</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD95D0DD-DDCC-4B30-89DE-4C16F690BDCB}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2">
+        <v>0.8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5603E0A7-EE30-4106-A0A2-BD27BB7E4C2A}">
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>10</v>
-      </c>
-      <c r="F2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>15</v>
-      </c>
-      <c r="F3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>10</v>
-      </c>
-      <c r="F4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>15</v>
-      </c>
-      <c r="F5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
+        <v>27</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>15</v>
-      </c>
-      <c r="F7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
+        <v>28</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
       </c>
       <c r="E8">
-        <v>10</v>
-      </c>
-      <c r="F8">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
+        <v>29</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
+      </c>
+      <c r="D9">
+        <v>15</v>
       </c>
       <c r="E9">
-        <v>15</v>
-      </c>
-      <c r="F9">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
       </c>
       <c r="E10">
-        <v>10</v>
-      </c>
-      <c r="F10">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11">
         <v>15</v>
       </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="E11">
-        <v>15</v>
-      </c>
-      <c r="F11">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
+        <v>32</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
       </c>
       <c r="E12">
-        <v>10</v>
-      </c>
-      <c r="F12">
         <v>1</v>
       </c>
     </row>
@@ -1239,40 +1611,229 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCB07F09-0C11-4BF9-8684-61C02A91D479}">
-  <dimension ref="A1:B3"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB08C565-83BE-4D2C-A1BF-F12C415DE0E2}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="20.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E03F24E-5078-49C6-979E-25F5315BC7A8}">
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46447</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3" s="1">
+        <v>46388</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5E169E81-15BD-449C-B092-143F386411C5}">
+          <x14:formula1>
+            <xm:f>'TP Parameters'!$A$2:$A$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C36ED19-8387-4E4C-BEB9-95A15048DC55}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="B2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3">
-        <v>80</v>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2">
+        <v>50.5</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46357</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{27BDE247-27BB-4269-9794-B9E3ABBD697E}">
+          <x14:formula1>
+            <xm:f>'TP Parameters'!$A$5:$A$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>